--- a/#HanKuang_anonymized.xlsx
+++ b/#HanKuang_anonymized.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8456,7 +8456,7 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10267,7 +10267,7 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10306,7 +10306,7 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11043,7 +11043,7 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11687,7 +11687,7 @@
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12142,7 +12142,7 @@
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13429,7 +13429,7 @@
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14586,7 +14586,7 @@
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14627,7 +14627,7 @@
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14671,7 +14671,7 @@
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15395,7 +15395,7 @@
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16823,7 +16823,7 @@
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17506,7 +17506,7 @@
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18241,7 +18241,7 @@
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20318,7 +20318,7 @@
       </c>
       <c r="J583" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21004,7 +21004,7 @@
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21042,7 +21042,7 @@
       </c>
       <c r="J605" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21083,7 +21083,7 @@
       </c>
       <c r="J606" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21761,7 +21761,7 @@
       </c>
       <c r="J627" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22458,7 +22458,7 @@
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23146,7 +23146,7 @@
       </c>
       <c r="J669" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23862,7 +23862,7 @@
       </c>
       <c r="J690" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23971,7 +23971,7 @@
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24659,7 +24659,7 @@
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25343,7 +25343,7 @@
       </c>
       <c r="J735" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26038,7 +26038,7 @@
       </c>
       <c r="J756" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26718,7 +26718,7 @@
       </c>
       <c r="J777" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26831,7 +26831,7 @@
       </c>
       <c r="J780" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27521,7 +27521,7 @@
       </c>
       <c r="J801" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27559,7 +27559,7 @@
       </c>
       <c r="J802" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28137,7 +28137,7 @@
       </c>
       <c r="J819" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28819,7 +28819,7 @@
       </c>
       <c r="J840" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29281,7 +29281,7 @@
       </c>
       <c r="J854" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29730,7 +29730,7 @@
       </c>
       <c r="J867" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
